--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jordan's River\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730F68E6-820D-433F-B9D7-BE11B693A4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DA89CF-B29C-4E58-B919-6D8268161E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDB69A35-D548-4CF0-946E-DFEC77257045}"/>
   </bookViews>
@@ -534,8 +534,8 @@
         <v>7.6331613054586773</v>
       </c>
       <c r="I2">
-        <f>_xlfn.STDEV.S(B2:B7, B9:B13)</f>
-        <v>7.8716984421175837</v>
+        <f>_xlfn.STDEV.S(B2:B8, B10:B13)</f>
+        <v>2.9076701075853588</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
